--- a/df_14.xlsx
+++ b/df_14.xlsx
@@ -710,10 +710,10 @@
         <v>2825</v>
       </c>
       <c r="AD2" t="n">
-        <v>20025</v>
+        <v>18900</v>
       </c>
       <c r="AE2" t="n">
-        <v>20013</v>
+        <v>18888</v>
       </c>
       <c r="AF2" t="b">
         <v>0</v>
@@ -839,10 +839,10 @@
         <v>2962</v>
       </c>
       <c r="AD3" t="n">
-        <v>600750</v>
+        <v>567000</v>
       </c>
       <c r="AE3" t="n">
-        <v>533680</v>
+        <v>499930</v>
       </c>
       <c r="AF3" t="b">
         <v>0</v>
@@ -968,10 +968,10 @@
         <v>2963</v>
       </c>
       <c r="AD4" t="n">
-        <v>310521</v>
+        <v>293076</v>
       </c>
       <c r="AE4" t="n">
-        <v>166001</v>
+        <v>148556</v>
       </c>
       <c r="AF4" t="b">
         <v>0</v>
@@ -1097,10 +1097,10 @@
         <v>5811</v>
       </c>
       <c r="AD5" t="n">
-        <v>213600</v>
+        <v>201600</v>
       </c>
       <c r="AE5" t="n">
-        <v>211200</v>
+        <v>199200</v>
       </c>
       <c r="AF5" t="b">
         <v>0</v>
@@ -1226,10 +1226,10 @@
         <v>9417</v>
       </c>
       <c r="AD6" t="n">
-        <v>3738</v>
+        <v>3528</v>
       </c>
       <c r="AE6" t="n">
-        <v>-1162</v>
+        <v>-1372</v>
       </c>
       <c r="AF6" t="b">
         <v>0</v>
@@ -1355,10 +1355,10 @@
         <v>9418</v>
       </c>
       <c r="AD7" t="n">
-        <v>3738</v>
+        <v>3528</v>
       </c>
       <c r="AE7" t="n">
-        <v>-1162</v>
+        <v>-1372</v>
       </c>
       <c r="AF7" t="b">
         <v>0</v>
@@ -1484,10 +1484,10 @@
         <v>9419</v>
       </c>
       <c r="AD8" t="n">
-        <v>2403</v>
+        <v>2268</v>
       </c>
       <c r="AE8" t="n">
-        <v>-1897</v>
+        <v>-2032</v>
       </c>
       <c r="AF8" t="b">
         <v>0</v>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1613,13 +1613,13 @@
         <v>9421</v>
       </c>
       <c r="AD9" t="n">
-        <v>5607</v>
+        <v>7056</v>
       </c>
       <c r="AE9" t="n">
-        <v>-1693</v>
+        <v>-244</v>
       </c>
       <c r="AF9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" t="n">
         <v>1042.857142857143</v>
@@ -1863,10 +1863,10 @@
         <v>12611</v>
       </c>
       <c r="AD11" t="n">
-        <v>26700</v>
+        <v>25200</v>
       </c>
       <c r="AE11" t="n">
-        <v>26600</v>
+        <v>25100</v>
       </c>
       <c r="AF11" t="b">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -2379,10 +2379,10 @@
         <v>15488</v>
       </c>
       <c r="AD15" t="n">
-        <v>211464</v>
+        <v>208656</v>
       </c>
       <c r="AE15" t="n">
-        <v>-5536</v>
+        <v>-8344</v>
       </c>
       <c r="AF15" t="b">
         <v>1</v>
@@ -2508,10 +2508,10 @@
         <v>17875</v>
       </c>
       <c r="AD16" t="n">
-        <v>28836</v>
+        <v>27216</v>
       </c>
       <c r="AE16" t="n">
-        <v>19536</v>
+        <v>17916</v>
       </c>
       <c r="AF16" t="b">
         <v>0</v>
@@ -2637,10 +2637,10 @@
         <v>19185</v>
       </c>
       <c r="AD17" t="n">
-        <v>347100</v>
+        <v>327600</v>
       </c>
       <c r="AE17" t="n">
-        <v>54100</v>
+        <v>34600</v>
       </c>
       <c r="AF17" t="b">
         <v>0</v>
@@ -2766,10 +2766,10 @@
         <v>21686</v>
       </c>
       <c r="AD18" t="n">
-        <v>3204</v>
+        <v>3024</v>
       </c>
       <c r="AE18" t="n">
-        <v>3192</v>
+        <v>3012</v>
       </c>
       <c r="AF18" t="b">
         <v>0</v>
@@ -2895,10 +2895,10 @@
         <v>22073</v>
       </c>
       <c r="AD19" t="n">
-        <v>2670000</v>
+        <v>2520000</v>
       </c>
       <c r="AE19" t="n">
-        <v>-330000</v>
+        <v>-480000</v>
       </c>
       <c r="AF19" t="b">
         <v>0</v>
